--- a/data/trans_dic/IP12B$diarrea-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$diarrea-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,16</t>
+          <t>0,0; 25,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,98</t>
+          <t>0,0; 35,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,24</t>
+          <t>0,0; 23,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,48; 54,41</t>
+          <t>6,56; 56,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,13</t>
+          <t>0,0; 15,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 29,39</t>
+          <t>4,8; 31,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,44</t>
+          <t>0,0; 17,16</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 37,78</t>
+          <t>4,29; 38,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,61</t>
+          <t>0,0; 22,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,13</t>
+          <t>0,0; 17,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,16</t>
+          <t>0,0; 28,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,19</t>
+          <t>0,0; 21,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 20,35</t>
+          <t>2,27; 19,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 18,24</t>
+          <t>1,96; 17,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,15</t>
+          <t>0,0; 9,72</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,96; 33,44</t>
+          <t>4,08; 32,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,66</t>
+          <t>0,0; 30,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,7; 38,57</t>
+          <t>4,47; 38,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,53</t>
+          <t>0,0; 41,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,75</t>
+          <t>0,0; 27,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,83</t>
+          <t>0,0; 30,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,52; 30,16</t>
+          <t>5,37; 28,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 19,79</t>
+          <t>2,23; 21,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 24,65</t>
+          <t>4,44; 24,08</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,31</t>
+          <t>0,0; 23,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,74</t>
+          <t>0,0; 30,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,45</t>
+          <t>0,0; 25,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,69</t>
+          <t>0,0; 20,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,78</t>
+          <t>0,0; 33,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,97</t>
+          <t>0,0; 15,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 17,68</t>
+          <t>1,71; 15,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 21,62</t>
+          <t>2,42; 21,52</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 16,44</t>
+          <t>3,53; 15,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,43; 14,81</t>
+          <t>3,11; 14,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 13,5</t>
+          <t>2,23; 13,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 15,5</t>
+          <t>2,82; 15,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,42; 18,66</t>
+          <t>5,23; 18,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 13,32</t>
+          <t>1,56; 14,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,09; 12,7</t>
+          <t>3,87; 12,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,33; 13,81</t>
+          <t>5,16; 13,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 11,29</t>
+          <t>3,25; 11,17</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1368</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2505</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>3874</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4315</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3117</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2749</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>670; 5758</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3654</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1312; 8588</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2744</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1687</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1291</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2374</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2590</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>519; 4627</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4366</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2774</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3995</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3345</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>640; 5419</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>653; 5914</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3483</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1742</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1882</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1422</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3110</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2122</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>518; 4189</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2910</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>518; 4474</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3412</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5009</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4820</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1127; 6068</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>613; 6011</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1222; 6630</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1180</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1386</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2207</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1921</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3681</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4339</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2692</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4424</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3097</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2761</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>627; 5860</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>571; 5086</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3430</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4108</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3679</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6684</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2807</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6800</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>10792</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>6486</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1551; 6800</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1903; 8644</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1229; 7367</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1315; 7394</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3324; 11862</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>748; 6722</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3509; 11239</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>6442; 17051</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3348; 11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$diarrea-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$diarrea-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -683,22 +683,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,17</t>
+          <t>0,0; 24,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,13</t>
+          <t>0,0; 35,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,32</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,56; 56,39</t>
+          <t>6,57; 53,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,21</t>
+          <t>0,0; 14,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 31,4</t>
+          <t>5,09; 29,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,16</t>
+          <t>0,0; 24,02</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,29; 38,26</t>
+          <t>4,23; 34,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,76</t>
+          <t>0,0; 20,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,32 +803,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,18</t>
+          <t>0,0; 21,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,28</t>
+          <t>0,0; 30,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,5</t>
+          <t>0,0; 20,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 19,19</t>
+          <t>1,87; 19,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 17,75</t>
+          <t>1,97; 18,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,72</t>
+          <t>0,0; 8,95</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 32,99</t>
+          <t>3,96; 34,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,9</t>
+          <t>0,0; 33,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,47; 38,59</t>
+          <t>4,63; 39,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,21</t>
+          <t>0,0; 47,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,65</t>
+          <t>0,0; 27,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,23</t>
+          <t>0,0; 27,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 28,93</t>
+          <t>5,76; 29,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 21,83</t>
+          <t>2,16; 19,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 24,08</t>
+          <t>4,77; 25,83</t>
         </is>
       </c>
     </row>
@@ -1013,42 +1013,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,67</t>
+          <t>0,0; 27,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,16</t>
+          <t>0,0; 25,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,65</t>
+          <t>0,0; 27,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,96</t>
+          <t>0,0; 21,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,52</t>
+          <t>0,0; 33,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,92</t>
+          <t>0,0; 18,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 15,99</t>
+          <t>1,73; 16,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 21,52</t>
+          <t>2,4; 21,0</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 15,5</t>
+          <t>2,65; 15,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 14,1</t>
+          <t>2,58; 13,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 13,36</t>
+          <t>3,05; 14,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,82; 15,83</t>
+          <t>2,83; 14,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 18,66</t>
+          <t>4,84; 17,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 14,05</t>
+          <t>1,58; 13,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,87; 12,41</t>
+          <t>4,04; 12,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,16; 13,66</t>
+          <t>5,23; 13,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,25; 11,17</t>
+          <t>3,19; 10,73</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1422,22 +1422,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4315</t>
+          <t>0; 4178</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3117</t>
+          <t>0; 3143</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2749</t>
+          <t>0; 2782</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>670; 5758</t>
+          <t>670; 5477</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3654</t>
+          <t>0; 3407</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1312; 8588</t>
+          <t>1393; 8003</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2744</t>
+          <t>0; 3841</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>519; 4627</t>
+          <t>512; 4146</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4366</t>
+          <t>0; 3992</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1595,32 +1595,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2774</t>
+          <t>0; 3426</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3995</t>
+          <t>0; 4267</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3345</t>
+          <t>0; 3246</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>640; 5419</t>
+          <t>529; 5461</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>653; 5914</t>
+          <t>655; 6022</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3483</t>
+          <t>0; 3207</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>518; 4189</t>
+          <t>503; 4381</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2910</t>
+          <t>0; 3174</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>518; 4474</t>
+          <t>536; 4590</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3412</t>
+          <t>0; 3922</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5009</t>
+          <t>0; 4915</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4820</t>
+          <t>0; 4357</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1127; 6068</t>
+          <t>1209; 6231</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>613; 6011</t>
+          <t>595; 5424</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1222; 6630</t>
+          <t>1313; 7112</t>
         </is>
       </c>
     </row>
@@ -1911,42 +1911,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3681</t>
+          <t>0; 4308</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4339</t>
+          <t>0; 3643</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2692</t>
+          <t>0; 2922</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4424</t>
+          <t>0; 4531</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3097</t>
+          <t>0; 3124</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2761</t>
+          <t>0; 3260</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>627; 5860</t>
+          <t>633; 5980</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>571; 5086</t>
+          <t>567; 4962</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1551; 6800</t>
+          <t>1161; 6945</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1903; 8644</t>
+          <t>1579; 8390</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1229; 7367</t>
+          <t>1679; 7863</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1315; 7394</t>
+          <t>1320; 6767</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3324; 11862</t>
+          <t>3074; 11413</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>748; 6722</t>
+          <t>755; 6453</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3509; 11239</t>
+          <t>3659; 11402</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6442; 17051</t>
+          <t>6535; 16554</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3348; 11500</t>
+          <t>3286; 11046</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$diarrea-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$diarrea-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24,53%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>7,98%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6,96%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>24,53%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 29,24</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6,48; 54,41</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 24,37</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 35,43</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 53,64</t>
+          <t>0,0; 25,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 29,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,18</t>
+          <t>0,0; 14,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,09; 29,26</t>
+          <t>4,86; 29,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,02</t>
+          <t>0,0; 23,44</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>13,95%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>6,73%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,2%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,23; 34,28</t>
+          <t>0,0; 24,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,81</t>
+          <t>0,0; 28,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 17,19</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4,21; 37,78</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 19,61</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 21,22</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 30,21</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 20,86</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 19,34</t>
+          <t>2,24; 20,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 18,08</t>
+          <t>1,94; 18,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,95</t>
+          <t>0,0; 9,15</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16,52%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,25%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8,92%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>13,72%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>6,66%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>16,24%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16,52%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,96; 34,51</t>
+          <t>0,0; 47,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,7</t>
+          <t>0,0; 24,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 39,59</t>
+          <t>0,0; 27,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,38</t>
+          <t>3,96; 33,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,13</t>
+          <t>0,0; 27,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,33</t>
+          <t>4,7; 38,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 29,71</t>
+          <t>5,52; 30,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 19,7</t>
+          <t>2,24; 19,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,77; 25,83</t>
+          <t>4,58; 24,65</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,57%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>5,28%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>8,2%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 31,45</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 20,69</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 39,78</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 27,7</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 25,32</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 27,84</t>
-        </is>
-      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,47</t>
+          <t>0,0; 30,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,81</t>
+          <t>0,0; 28,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,8</t>
+          <t>0,0; 20,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 16,31</t>
+          <t>1,77; 17,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 21,0</t>
+          <t>2,45; 21,62</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10,52%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>7,82%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>6,7%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>6,67%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10,52%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 15,83</t>
+          <t>2,8; 15,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 13,69</t>
+          <t>4,42; 18,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 14,26</t>
+          <t>1,61; 13,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,83; 14,49</t>
+          <t>3,47; 16,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,84; 17,96</t>
+          <t>2,43; 14,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 13,48</t>
+          <t>2,55; 13,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 12,59</t>
+          <t>4,09; 12,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 13,26</t>
+          <t>5,33; 13,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,19; 10,73</t>
+          <t>3,23; 11,29</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2505</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1368</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>617</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2505</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 3447</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>661; 5556</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4178</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3143</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2782</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>670; 5477</t>
+          <t>0; 4314</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2660</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3407</t>
+          <t>0; 3394</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1393; 8003</t>
+          <t>1330; 8038</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3841</t>
+          <t>0; 3748</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1687</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1291</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1299</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>512; 4146</t>
+          <t>0; 3896</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3992</t>
+          <t>0; 3978</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0; 2674</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>509; 4569</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3762</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3426</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4267</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3246</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>529; 5461</t>
+          <t>633; 5748</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>655; 6022</t>
+          <t>647; 6074</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3207</t>
+          <t>0; 3280</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1422</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1742</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1882</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1367</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1494</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1422</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>503; 4381</t>
+          <t>0; 3935</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3174</t>
+          <t>0; 4484</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536; 4590</t>
+          <t>0; 4437</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3922</t>
+          <t>502; 4246</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4915</t>
+          <t>0; 2604</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4357</t>
+          <t>545; 4472</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1209; 6231</t>
+          <t>1158; 6327</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>595; 5424</t>
+          <t>617; 5449</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1313; 7112</t>
+          <t>1261; 6787</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1386</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>822</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1180</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1386</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>0; 3300</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4367</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3676</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>0; 4308</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0; 3643</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0; 2922</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4531</t>
+          <t>0; 4714</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3124</t>
+          <t>0; 4135</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3260</t>
+          <t>0; 3635</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>633; 5980</t>
+          <t>650; 6480</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>567; 4962</t>
+          <t>579; 5107</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6684</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2807</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>3430</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>4108</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3679</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3370</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6684</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2807</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1161; 6945</t>
+          <t>1308; 7239</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1579; 8390</t>
+          <t>2807; 11859</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1679; 7863</t>
+          <t>772; 6375</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1320; 6767</t>
+          <t>1525; 7215</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3074; 11413</t>
+          <t>1487; 9075</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>755; 6453</t>
+          <t>1408; 7444</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3659; 11402</t>
+          <t>3704; 11500</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6535; 16554</t>
+          <t>6653; 17248</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3286; 11046</t>
+          <t>3330; 11631</t>
         </is>
       </c>
     </row>
